--- a/docs/채집_확률표.xlsx
+++ b/docs/채집_확률표.xlsx
@@ -2326,11 +2326,11 @@
         <v>8</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E2" s="4" t="n">
         <f aca="false">D2/SUM($D$2:$D$13)</f>
-        <v>0.291970802919708</v>
+        <v>0.192592592592593</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
@@ -2347,11 +2347,11 @@
         <v>8</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E3" s="4" t="n">
         <f aca="false">D3/SUM($D$2:$D$13)</f>
-        <v>0.145985401459854</v>
+        <v>0.0962962962962963</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>9</v>
@@ -2368,11 +2368,11 @@
         <v>8</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E4" s="4" t="n">
         <f aca="false">D4/SUM($D$2:$D$13)</f>
-        <v>0.109489051094891</v>
+        <v>0.0740740740740741</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>12</v>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">D5/SUM($D$2:$D$13)</f>
-        <v>0.072992700729927</v>
+        <v>0.0740740740740741</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>12</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="E6" s="4" t="n">
         <f aca="false">D6/SUM($D$2:$D$13)</f>
-        <v>0.0583941605839416</v>
+        <v>0.0592592592592593</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>12</v>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="E7" s="4" t="n">
         <f aca="false">D7/SUM($D$2:$D$13)</f>
-        <v>0.0218978102189781</v>
+        <v>0.0222222222222222</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>12</v>
@@ -2452,11 +2452,11 @@
         <v>8</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" s="4" t="n">
         <f aca="false">D8/SUM($D$2:$D$13)</f>
-        <v>0.0291970802919708</v>
+        <v>0.0444444444444444</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>12</v>
@@ -2473,11 +2473,11 @@
         <v>19</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E9" s="4" t="n">
         <f aca="false">D9/SUM($D$2:$D$13)</f>
-        <v>0.102189781021898</v>
+        <v>0.192592592592593</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>12</v>
@@ -2494,11 +2494,11 @@
         <v>19</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E10" s="4" t="n">
         <f aca="false">D10/SUM($D$2:$D$13)</f>
-        <v>0.072992700729927</v>
+        <v>0.148148148148148</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>12</v>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="E11" s="4" t="n">
         <f aca="false">D11/SUM($D$2:$D$13)</f>
-        <v>0.0364963503649635</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>12</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="E12" s="4" t="n">
         <f aca="false">D12/SUM($D$2:$D$13)</f>
-        <v>0.0291970802919708</v>
+        <v>0.0296296296296296</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>12</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E13" s="4" t="n">
         <f aca="false">D13/SUM($D$2:$D$13)</f>
-        <v>0.0291970802919708</v>
+        <v>0.0296296296296296</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>12</v>
@@ -2575,7 +2575,7 @@
       <c r="C14" s="7"/>
       <c r="D14" s="6" t="n">
         <f aca="false">SUM(D2:D13)</f>
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E14" s="8" t="n">
         <f aca="false">SUM(E2:E13)</f>
@@ -2594,11 +2594,11 @@
         <v>8</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E16" s="4" t="n">
         <f aca="false">D16/SUM($D$16:$D$24)</f>
-        <v>0.306569343065693</v>
+        <v>0.206106870229008</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>12</v>
@@ -2615,11 +2615,11 @@
         <v>8</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E17" s="4" t="n">
         <f aca="false">D17/SUM($D$16:$D$24)</f>
-        <v>0.255474452554745</v>
+        <v>0.175572519083969</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>9</v>
@@ -2636,11 +2636,11 @@
         <v>8</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E18" s="4" t="n">
         <f aca="false">D18/SUM($D$16:$D$24)</f>
-        <v>0.0875912408759124</v>
+        <v>0.137404580152672</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>12</v>
@@ -2657,11 +2657,11 @@
         <v>8</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E19" s="4" t="n">
         <f aca="false">D19/SUM($D$16:$D$24)</f>
-        <v>0.0802919708029197</v>
+        <v>0.0534351145038168</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>9</v>
@@ -2678,11 +2678,11 @@
         <v>19</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E20" s="4" t="n">
         <f aca="false">D20/SUM($D$16:$D$24)</f>
-        <v>0.102189781021898</v>
+        <v>0.198473282442748</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>12</v>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="E21" s="4" t="n">
         <f aca="false">D21/SUM($D$16:$D$24)</f>
-        <v>0.072992700729927</v>
+        <v>0.0763358778625954</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>12</v>
@@ -2720,11 +2720,11 @@
         <v>19</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E22" s="4" t="n">
         <f aca="false">D22/SUM($D$16:$D$24)</f>
-        <v>0.0364963503649635</v>
+        <v>0.0916030534351145</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>12</v>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="E23" s="4" t="n">
         <f aca="false">D23/SUM($D$16:$D$24)</f>
-        <v>0.0291970802919708</v>
+        <v>0.0305343511450382</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>12</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="E24" s="4" t="n">
         <f aca="false">D24/SUM($D$16:$D$24)</f>
-        <v>0.0291970802919708</v>
+        <v>0.0305343511450382</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>12</v>
@@ -2780,7 +2780,7 @@
       <c r="C25" s="7"/>
       <c r="D25" s="6" t="n">
         <f aca="false">SUM(D16:D24)</f>
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E25" s="8" t="n">
         <f aca="false">SUM(E16:E24)</f>
@@ -2799,11 +2799,11 @@
         <v>8</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E27" s="4" t="n">
         <f aca="false">D27/SUM($D$27:$D$36)</f>
-        <v>0.328467153284672</v>
+        <v>0.218045112781955</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>9</v>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E28" s="4" t="n">
         <f aca="false">D28/SUM($D$27:$D$36)</f>
-        <v>0.131386861313869</v>
+        <v>0.135338345864662</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>12</v>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="E29" s="4" t="n">
         <f aca="false">D29/SUM($D$27:$D$36)</f>
-        <v>0.116788321167883</v>
+        <v>0.120300751879699</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>12</v>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E30" s="4" t="n">
         <f aca="false">D30/SUM($D$27:$D$36)</f>
-        <v>0.0583941605839416</v>
+        <v>0.0601503759398496</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>12</v>
@@ -2883,11 +2883,11 @@
         <v>8</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E31" s="4" t="n">
         <f aca="false">D31/SUM($D$27:$D$36)</f>
-        <v>0.0948905109489051</v>
+        <v>0.0601503759398496</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>12</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="E32" s="4" t="n">
         <f aca="false">D32/SUM($D$27:$D$36)</f>
-        <v>0.102189781021898</v>
+        <v>0.105263157894737</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>12</v>
@@ -2925,11 +2925,11 @@
         <v>19</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E33" s="4" t="n">
         <f aca="false">D33/SUM($D$27:$D$36)</f>
-        <v>0.072992700729927</v>
+        <v>0.150375939849624</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>12</v>
@@ -2946,11 +2946,11 @@
         <v>19</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E34" s="4" t="n">
         <f aca="false">D34/SUM($D$27:$D$36)</f>
-        <v>0.0364963503649635</v>
+        <v>0.0902255639097744</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>12</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E35" s="4" t="n">
         <f aca="false">D35/SUM($D$27:$D$36)</f>
-        <v>0.0291970802919708</v>
+        <v>0.0300751879699248</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>12</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="E36" s="4" t="n">
         <f aca="false">D36/SUM($D$27:$D$36)</f>
-        <v>0.0291970802919708</v>
+        <v>0.0300751879699248</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>12</v>
@@ -3006,7 +3006,7 @@
       <c r="C37" s="7"/>
       <c r="D37" s="6" t="n">
         <f aca="false">SUM(D27:D36)</f>
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E37" s="8" t="n">
         <f aca="false">SUM(E27:E36)</f>
@@ -3025,11 +3025,11 @@
         <v>8</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E39" s="4" t="n">
         <f aca="false">D39/SUM($D$39:$D$48)</f>
-        <v>0.310077519379845</v>
+        <v>0.2</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>9</v>
@@ -3046,11 +3046,11 @@
         <v>8</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E40" s="4" t="n">
         <f aca="false">D40/SUM($D$39:$D$48)</f>
-        <v>0.108527131782946</v>
+        <v>0.0692307692307692</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>12</v>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="E41" s="4" t="n">
         <f aca="false">D41/SUM($D$39:$D$48)</f>
-        <v>0.0387596899224806</v>
+        <v>0.0384615384615385</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>12</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="E42" s="4" t="n">
         <f aca="false">D42/SUM($D$39:$D$48)</f>
-        <v>0.0465116279069767</v>
+        <v>0.0461538461538462</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>12</v>
@@ -3109,11 +3109,11 @@
         <v>8</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E43" s="4" t="n">
         <f aca="false">D43/SUM($D$39:$D$48)</f>
-        <v>0.209302325581395</v>
+        <v>0.138461538461538</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>9</v>
@@ -3130,11 +3130,11 @@
         <v>19</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E44" s="4" t="n">
         <f aca="false">D44/SUM($D$39:$D$48)</f>
-        <v>0.108527131782946</v>
+        <v>0.2</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>12</v>
@@ -3151,11 +3151,11 @@
         <v>19</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E45" s="4" t="n">
         <f aca="false">D45/SUM($D$39:$D$48)</f>
-        <v>0.0775193798449612</v>
+        <v>0.153846153846154</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>12</v>
@@ -3172,11 +3172,11 @@
         <v>19</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E46" s="4" t="n">
         <f aca="false">D46/SUM($D$39:$D$48)</f>
-        <v>0.0387596899224806</v>
+        <v>0.0923076923076923</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>12</v>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="E47" s="4" t="n">
         <f aca="false">D47/SUM($D$39:$D$48)</f>
-        <v>0.0310077519379845</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>12</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="E48" s="4" t="n">
         <f aca="false">D48/SUM($D$39:$D$48)</f>
-        <v>0.0310077519379845</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>12</v>
@@ -3232,7 +3232,7 @@
       <c r="C49" s="7"/>
       <c r="D49" s="6" t="n">
         <f aca="false">SUM(D39:D48)</f>
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E49" s="8" t="n">
         <f aca="false">SUM(E39:E48)</f>
@@ -3251,11 +3251,11 @@
         <v>8</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E51" s="4" t="n">
         <f aca="false">D51/SUM($D$51:$D$60)</f>
-        <v>0.233576642335766</v>
+        <v>0.147887323943662</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>12</v>
@@ -3272,11 +3272,11 @@
         <v>8</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E52" s="4" t="n">
         <f aca="false">D52/SUM($D$51:$D$60)</f>
-        <v>0.218978102189781</v>
+        <v>0.140845070422535</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>9</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="E53" s="4" t="n">
         <f aca="false">D53/SUM($D$51:$D$60)</f>
-        <v>0.102189781021898</v>
+        <v>0.0985915492957746</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>12</v>
@@ -3314,11 +3314,11 @@
         <v>8</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E54" s="4" t="n">
         <f aca="false">D54/SUM($D$51:$D$60)</f>
-        <v>0.131386861313869</v>
+        <v>0.0845070422535211</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>9</v>
@@ -3335,11 +3335,11 @@
         <v>8</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E55" s="4" t="n">
         <f aca="false">D55/SUM($D$51:$D$60)</f>
-        <v>0.0437956204379562</v>
+        <v>0.0633802816901408</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>12</v>
@@ -3356,11 +3356,11 @@
         <v>19</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E56" s="4" t="n">
         <f aca="false">D56/SUM($D$51:$D$60)</f>
-        <v>0.102189781021898</v>
+        <v>0.183098591549296</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>12</v>
@@ -3377,11 +3377,11 @@
         <v>19</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E57" s="4" t="n">
         <f aca="false">D57/SUM($D$51:$D$60)</f>
-        <v>0.072992700729927</v>
+        <v>0.140845070422535</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>12</v>
@@ -3398,11 +3398,11 @@
         <v>19</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E58" s="4" t="n">
         <f aca="false">D58/SUM($D$51:$D$60)</f>
-        <v>0.0364963503649635</v>
+        <v>0.0845070422535211</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>12</v>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="E59" s="4" t="n">
         <f aca="false">D59/SUM($D$51:$D$60)</f>
-        <v>0.0291970802919708</v>
+        <v>0.028169014084507</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>12</v>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="E60" s="4" t="n">
         <f aca="false">D60/SUM($D$51:$D$60)</f>
-        <v>0.0291970802919708</v>
+        <v>0.028169014084507</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>12</v>
@@ -3458,7 +3458,7 @@
       <c r="C61" s="7"/>
       <c r="D61" s="6" t="n">
         <f aca="false">SUM(D51:D60)</f>
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E61" s="8" t="n">
         <f aca="false">SUM(E51:E60)</f>
@@ -3477,11 +3477,11 @@
         <v>8</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E63" s="4" t="n">
         <f aca="false">D63/SUM($D$63:$D$71)</f>
-        <v>0.35036496350365</v>
+        <v>0.208053691275168</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>9</v>
@@ -3498,11 +3498,11 @@
         <v>8</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E64" s="4" t="n">
         <f aca="false">D64/SUM($D$63:$D$71)</f>
-        <v>0.102189781021898</v>
+        <v>0.140939597315436</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>12</v>
@@ -3519,11 +3519,11 @@
         <v>8</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E65" s="4" t="n">
         <f aca="false">D65/SUM($D$63:$D$71)</f>
-        <v>0.145985401459854</v>
+        <v>0.087248322147651</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>12</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="E66" s="4" t="n">
         <f aca="false">D66/SUM($D$63:$D$71)</f>
-        <v>0.131386861313869</v>
+        <v>0.120805369127517</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>12</v>
@@ -3561,11 +3561,11 @@
         <v>19</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E67" s="4" t="n">
         <f aca="false">D67/SUM($D$63:$D$71)</f>
-        <v>0.102189781021898</v>
+        <v>0.174496644295302</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>12</v>
@@ -3582,11 +3582,11 @@
         <v>19</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E68" s="4" t="n">
         <f aca="false">D68/SUM($D$63:$D$71)</f>
-        <v>0.072992700729927</v>
+        <v>0.134228187919463</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>12</v>
@@ -3603,11 +3603,11 @@
         <v>19</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E69" s="4" t="n">
         <f aca="false">D69/SUM($D$63:$D$71)</f>
-        <v>0.0364963503649635</v>
+        <v>0.0805369127516779</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>12</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="E70" s="4" t="n">
         <f aca="false">D70/SUM($D$63:$D$71)</f>
-        <v>0.0291970802919708</v>
+        <v>0.0268456375838926</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>12</v>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="E71" s="4" t="n">
         <f aca="false">D71/SUM($D$63:$D$71)</f>
-        <v>0.0291970802919708</v>
+        <v>0.0268456375838926</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>12</v>
@@ -3663,7 +3663,7 @@
       <c r="C72" s="7"/>
       <c r="D72" s="6" t="n">
         <f aca="false">SUM(D63:D71)</f>
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="E72" s="8" t="n">
         <f aca="false">SUM(E63:E71)</f>
@@ -3936,15 +3936,15 @@
       </c>
       <c r="C5" s="20" t="n">
         <f aca="false">'채집 확률표'!E2</f>
-        <v>0.291970802919708</v>
+        <v>0.192592592592593</v>
       </c>
       <c r="D5" s="21" t="n">
         <f aca="false">C5*규칙!$B$12*규칙!$B$8</f>
-        <v>0.656934306569343</v>
+        <v>0.433333333333333</v>
       </c>
       <c r="E5" s="22" t="n">
         <f aca="false">D5*$B$2</f>
-        <v>4.5985401459854</v>
+        <v>3.03333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3956,15 +3956,15 @@
       </c>
       <c r="C6" s="20" t="n">
         <f aca="false">'채집 확률표'!E3</f>
-        <v>0.145985401459854</v>
+        <v>0.0962962962962963</v>
       </c>
       <c r="D6" s="21" t="n">
         <f aca="false">C6*규칙!$B$12*규칙!$B$8</f>
-        <v>0.328467153284672</v>
+        <v>0.216666666666667</v>
       </c>
       <c r="E6" s="22" t="n">
         <f aca="false">D6*$B$2</f>
-        <v>2.2992700729927</v>
+        <v>1.51666666666667</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3976,15 +3976,15 @@
       </c>
       <c r="C7" s="20" t="n">
         <f aca="false">'채집 확률표'!E4</f>
-        <v>0.109489051094891</v>
+        <v>0.0740740740740741</v>
       </c>
       <c r="D7" s="21" t="n">
         <f aca="false">C7*규칙!$B$12*1</f>
-        <v>0.164233576642336</v>
+        <v>0.111111111111111</v>
       </c>
       <c r="E7" s="22" t="n">
         <f aca="false">D7*$B$2</f>
-        <v>1.14963503649635</v>
+        <v>0.777777777777778</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3996,15 +3996,15 @@
       </c>
       <c r="C8" s="20" t="n">
         <f aca="false">'채집 확률표'!E5</f>
-        <v>0.072992700729927</v>
+        <v>0.0740740740740741</v>
       </c>
       <c r="D8" s="21" t="n">
         <f aca="false">C8*규칙!$B$12*1</f>
-        <v>0.109489051094891</v>
+        <v>0.111111111111111</v>
       </c>
       <c r="E8" s="22" t="n">
         <f aca="false">D8*$B$2</f>
-        <v>0.766423357664234</v>
+        <v>0.777777777777778</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4016,15 +4016,15 @@
       </c>
       <c r="C9" s="20" t="n">
         <f aca="false">'채집 확률표'!E6</f>
-        <v>0.0583941605839416</v>
+        <v>0.0592592592592593</v>
       </c>
       <c r="D9" s="21" t="n">
         <f aca="false">C9*규칙!$B$12*1</f>
-        <v>0.0875912408759124</v>
+        <v>0.0888888888888889</v>
       </c>
       <c r="E9" s="22" t="n">
         <f aca="false">D9*$B$2</f>
-        <v>0.613138686131387</v>
+        <v>0.622222222222222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4036,15 +4036,15 @@
       </c>
       <c r="C10" s="20" t="n">
         <f aca="false">'채집 확률표'!E7</f>
-        <v>0.0218978102189781</v>
+        <v>0.0222222222222222</v>
       </c>
       <c r="D10" s="21" t="n">
         <f aca="false">C10*규칙!$B$12*1</f>
-        <v>0.0328467153284672</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="E10" s="22" t="n">
         <f aca="false">D10*$B$2</f>
-        <v>0.22992700729927</v>
+        <v>0.233333333333333</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4056,15 +4056,15 @@
       </c>
       <c r="C11" s="20" t="n">
         <f aca="false">'채집 확률표'!E8</f>
-        <v>0.0291970802919708</v>
+        <v>0.0444444444444444</v>
       </c>
       <c r="D11" s="21" t="n">
         <f aca="false">C11*규칙!$B$12*1</f>
-        <v>0.0437956204379562</v>
+        <v>0.0666666666666667</v>
       </c>
       <c r="E11" s="22" t="n">
         <f aca="false">D11*$B$2</f>
-        <v>0.306569343065693</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4076,15 +4076,15 @@
       </c>
       <c r="C12" s="20" t="n">
         <f aca="false">'채집 확률표'!E9</f>
-        <v>0.102189781021898</v>
+        <v>0.192592592592593</v>
       </c>
       <c r="D12" s="21" t="n">
         <f aca="false">C12*규칙!$B$12*1</f>
-        <v>0.153284671532847</v>
+        <v>0.288888888888889</v>
       </c>
       <c r="E12" s="22" t="n">
         <f aca="false">D12*$B$2</f>
-        <v>1.07299270072993</v>
+        <v>2.02222222222222</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4096,15 +4096,15 @@
       </c>
       <c r="C13" s="20" t="n">
         <f aca="false">'채집 확률표'!E10</f>
-        <v>0.072992700729927</v>
+        <v>0.148148148148148</v>
       </c>
       <c r="D13" s="21" t="n">
         <f aca="false">C13*규칙!$B$12*1</f>
-        <v>0.109489051094891</v>
+        <v>0.222222222222222</v>
       </c>
       <c r="E13" s="22" t="n">
         <f aca="false">D13*$B$2</f>
-        <v>0.766423357664234</v>
+        <v>1.55555555555556</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4116,15 +4116,15 @@
       </c>
       <c r="C14" s="20" t="n">
         <f aca="false">'채집 확률표'!E11</f>
-        <v>0.0364963503649635</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D14" s="21" t="n">
         <f aca="false">C14*규칙!$B$12*1</f>
-        <v>0.0547445255474453</v>
+        <v>0.0555555555555556</v>
       </c>
       <c r="E14" s="22" t="n">
         <f aca="false">D14*$B$2</f>
-        <v>0.383211678832117</v>
+        <v>0.388888888888889</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4136,15 +4136,15 @@
       </c>
       <c r="C15" s="20" t="n">
         <f aca="false">'채집 확률표'!E12</f>
-        <v>0.0291970802919708</v>
+        <v>0.0296296296296296</v>
       </c>
       <c r="D15" s="21" t="n">
         <f aca="false">C15*규칙!$B$12*1</f>
-        <v>0.0437956204379562</v>
+        <v>0.0444444444444444</v>
       </c>
       <c r="E15" s="22" t="n">
         <f aca="false">D15*$B$2</f>
-        <v>0.306569343065693</v>
+        <v>0.311111111111111</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4156,15 +4156,15 @@
       </c>
       <c r="C16" s="20" t="n">
         <f aca="false">'채집 확률표'!E13</f>
-        <v>0.0291970802919708</v>
+        <v>0.0296296296296296</v>
       </c>
       <c r="D16" s="21" t="n">
         <f aca="false">C16*규칙!$B$12*1</f>
-        <v>0.0437956204379562</v>
+        <v>0.0444444444444444</v>
       </c>
       <c r="E16" s="22" t="n">
         <f aca="false">D16*$B$2</f>
-        <v>0.306569343065693</v>
+        <v>0.311111111111111</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4176,15 +4176,15 @@
       </c>
       <c r="C18" s="20" t="n">
         <f aca="false">'채집 확률표'!E16</f>
-        <v>0.306569343065693</v>
+        <v>0.206106870229008</v>
       </c>
       <c r="D18" s="21" t="n">
         <f aca="false">C18*규칙!$B$12*1</f>
-        <v>0.45985401459854</v>
+        <v>0.309160305343511</v>
       </c>
       <c r="E18" s="22" t="n">
         <f aca="false">D18*$B$2</f>
-        <v>3.21897810218978</v>
+        <v>2.16412213740458</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4196,15 +4196,15 @@
       </c>
       <c r="C19" s="20" t="n">
         <f aca="false">'채집 확률표'!E17</f>
-        <v>0.255474452554745</v>
+        <v>0.175572519083969</v>
       </c>
       <c r="D19" s="21" t="n">
         <f aca="false">C19*규칙!$B$12*규칙!$B$8</f>
-        <v>0.574817518248175</v>
+        <v>0.395038167938931</v>
       </c>
       <c r="E19" s="22" t="n">
         <f aca="false">D19*$B$2</f>
-        <v>4.02372262773723</v>
+        <v>2.76526717557252</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4216,15 +4216,15 @@
       </c>
       <c r="C20" s="20" t="n">
         <f aca="false">'채집 확률표'!E18</f>
-        <v>0.0875912408759124</v>
+        <v>0.137404580152672</v>
       </c>
       <c r="D20" s="21" t="n">
         <f aca="false">C20*규칙!$B$12*1</f>
-        <v>0.131386861313869</v>
+        <v>0.206106870229008</v>
       </c>
       <c r="E20" s="22" t="n">
         <f aca="false">D20*$B$2</f>
-        <v>0.91970802919708</v>
+        <v>1.44274809160305</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4236,15 +4236,15 @@
       </c>
       <c r="C21" s="20" t="n">
         <f aca="false">'채집 확률표'!E19</f>
-        <v>0.0802919708029197</v>
+        <v>0.0534351145038168</v>
       </c>
       <c r="D21" s="21" t="n">
         <f aca="false">C21*규칙!$B$12*규칙!$B$8</f>
-        <v>0.180656934306569</v>
+        <v>0.120229007633588</v>
       </c>
       <c r="E21" s="22" t="n">
         <f aca="false">D21*$B$2</f>
-        <v>1.26459854014599</v>
+        <v>0.841603053435114</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4256,15 +4256,15 @@
       </c>
       <c r="C22" s="20" t="n">
         <f aca="false">'채집 확률표'!E20</f>
-        <v>0.102189781021898</v>
+        <v>0.198473282442748</v>
       </c>
       <c r="D22" s="21" t="n">
         <f aca="false">C22*규칙!$B$12*1</f>
-        <v>0.153284671532847</v>
+        <v>0.297709923664122</v>
       </c>
       <c r="E22" s="22" t="n">
         <f aca="false">D22*$B$2</f>
-        <v>1.07299270072993</v>
+        <v>2.08396946564885</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4276,15 +4276,15 @@
       </c>
       <c r="C23" s="20" t="n">
         <f aca="false">'채집 확률표'!E21</f>
-        <v>0.072992700729927</v>
+        <v>0.0763358778625954</v>
       </c>
       <c r="D23" s="21" t="n">
         <f aca="false">C23*규칙!$B$12*1</f>
-        <v>0.109489051094891</v>
+        <v>0.114503816793893</v>
       </c>
       <c r="E23" s="22" t="n">
         <f aca="false">D23*$B$2</f>
-        <v>0.766423357664234</v>
+        <v>0.801526717557252</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4296,15 +4296,15 @@
       </c>
       <c r="C24" s="20" t="n">
         <f aca="false">'채집 확률표'!E22</f>
-        <v>0.0364963503649635</v>
+        <v>0.0916030534351145</v>
       </c>
       <c r="D24" s="21" t="n">
         <f aca="false">C24*규칙!$B$12*1</f>
-        <v>0.0547445255474453</v>
+        <v>0.137404580152672</v>
       </c>
       <c r="E24" s="22" t="n">
         <f aca="false">D24*$B$2</f>
-        <v>0.383211678832117</v>
+        <v>0.961832061068702</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4316,15 +4316,15 @@
       </c>
       <c r="C25" s="20" t="n">
         <f aca="false">'채집 확률표'!E23</f>
-        <v>0.0291970802919708</v>
+        <v>0.0305343511450382</v>
       </c>
       <c r="D25" s="21" t="n">
         <f aca="false">C25*규칙!$B$12*1</f>
-        <v>0.0437956204379562</v>
+        <v>0.0458015267175573</v>
       </c>
       <c r="E25" s="22" t="n">
         <f aca="false">D25*$B$2</f>
-        <v>0.306569343065693</v>
+        <v>0.320610687022901</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4336,15 +4336,15 @@
       </c>
       <c r="C26" s="20" t="n">
         <f aca="false">'채집 확률표'!E24</f>
-        <v>0.0291970802919708</v>
+        <v>0.0305343511450382</v>
       </c>
       <c r="D26" s="21" t="n">
         <f aca="false">C26*규칙!$B$12*1</f>
-        <v>0.0437956204379562</v>
+        <v>0.0458015267175573</v>
       </c>
       <c r="E26" s="22" t="n">
         <f aca="false">D26*$B$2</f>
-        <v>0.306569343065693</v>
+        <v>0.320610687022901</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4356,15 +4356,15 @@
       </c>
       <c r="C28" s="20" t="n">
         <f aca="false">'채집 확률표'!E27</f>
-        <v>0.328467153284672</v>
+        <v>0.218045112781955</v>
       </c>
       <c r="D28" s="21" t="n">
         <f aca="false">C28*규칙!$B$12*규칙!$B$8</f>
-        <v>0.739051094890511</v>
+        <v>0.490601503759398</v>
       </c>
       <c r="E28" s="22" t="n">
         <f aca="false">D28*$B$2</f>
-        <v>5.17335766423358</v>
+        <v>3.43421052631579</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4376,15 +4376,15 @@
       </c>
       <c r="C29" s="20" t="n">
         <f aca="false">'채집 확률표'!E28</f>
-        <v>0.131386861313869</v>
+        <v>0.135338345864662</v>
       </c>
       <c r="D29" s="21" t="n">
         <f aca="false">C29*규칙!$B$12*1</f>
-        <v>0.197080291970803</v>
+        <v>0.203007518796992</v>
       </c>
       <c r="E29" s="22" t="n">
         <f aca="false">D29*$B$2</f>
-        <v>1.37956204379562</v>
+        <v>1.42105263157895</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4396,15 +4396,15 @@
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">'채집 확률표'!E29</f>
-        <v>0.116788321167883</v>
+        <v>0.120300751879699</v>
       </c>
       <c r="D30" s="21" t="n">
         <f aca="false">C30*규칙!$B$12*1</f>
-        <v>0.175182481751825</v>
+        <v>0.180451127819549</v>
       </c>
       <c r="E30" s="22" t="n">
         <f aca="false">D30*$B$2</f>
-        <v>1.22627737226277</v>
+        <v>1.26315789473684</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4416,15 +4416,15 @@
       </c>
       <c r="C31" s="20" t="n">
         <f aca="false">'채집 확률표'!E30</f>
-        <v>0.0583941605839416</v>
+        <v>0.0601503759398496</v>
       </c>
       <c r="D31" s="21" t="n">
         <f aca="false">C31*규칙!$B$12*1</f>
-        <v>0.0875912408759124</v>
+        <v>0.0902255639097744</v>
       </c>
       <c r="E31" s="22" t="n">
         <f aca="false">D31*$B$2</f>
-        <v>0.613138686131387</v>
+        <v>0.631578947368421</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4436,15 +4436,15 @@
       </c>
       <c r="C32" s="20" t="n">
         <f aca="false">'채집 확률표'!E31</f>
-        <v>0.0948905109489051</v>
+        <v>0.0601503759398496</v>
       </c>
       <c r="D32" s="21" t="n">
         <f aca="false">C32*규칙!$B$12*1</f>
-        <v>0.142335766423358</v>
+        <v>0.0902255639097744</v>
       </c>
       <c r="E32" s="22" t="n">
         <f aca="false">D32*$B$2</f>
-        <v>0.996350364963504</v>
+        <v>0.631578947368421</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4456,15 +4456,15 @@
       </c>
       <c r="C33" s="20" t="n">
         <f aca="false">'채집 확률표'!E32</f>
-        <v>0.102189781021898</v>
+        <v>0.105263157894737</v>
       </c>
       <c r="D33" s="21" t="n">
         <f aca="false">C33*규칙!$B$12*1</f>
-        <v>0.153284671532847</v>
+        <v>0.157894736842105</v>
       </c>
       <c r="E33" s="22" t="n">
         <f aca="false">D33*$B$2</f>
-        <v>1.07299270072993</v>
+        <v>1.10526315789474</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4476,15 +4476,15 @@
       </c>
       <c r="C34" s="20" t="n">
         <f aca="false">'채집 확률표'!E33</f>
-        <v>0.072992700729927</v>
+        <v>0.150375939849624</v>
       </c>
       <c r="D34" s="21" t="n">
         <f aca="false">C34*규칙!$B$12*1</f>
-        <v>0.109489051094891</v>
+        <v>0.225563909774436</v>
       </c>
       <c r="E34" s="22" t="n">
         <f aca="false">D34*$B$2</f>
-        <v>0.766423357664234</v>
+        <v>1.57894736842105</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4496,15 +4496,15 @@
       </c>
       <c r="C35" s="20" t="n">
         <f aca="false">'채집 확률표'!E34</f>
-        <v>0.0364963503649635</v>
+        <v>0.0902255639097744</v>
       </c>
       <c r="D35" s="21" t="n">
         <f aca="false">C35*규칙!$B$12*1</f>
-        <v>0.0547445255474453</v>
+        <v>0.135338345864662</v>
       </c>
       <c r="E35" s="22" t="n">
         <f aca="false">D35*$B$2</f>
-        <v>0.383211678832117</v>
+        <v>0.947368421052632</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4516,15 +4516,15 @@
       </c>
       <c r="C36" s="20" t="n">
         <f aca="false">'채집 확률표'!E35</f>
-        <v>0.0291970802919708</v>
+        <v>0.0300751879699248</v>
       </c>
       <c r="D36" s="21" t="n">
         <f aca="false">C36*규칙!$B$12*1</f>
-        <v>0.0437956204379562</v>
+        <v>0.0451127819548872</v>
       </c>
       <c r="E36" s="22" t="n">
         <f aca="false">D36*$B$2</f>
-        <v>0.306569343065693</v>
+        <v>0.315789473684211</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4536,15 +4536,15 @@
       </c>
       <c r="C37" s="20" t="n">
         <f aca="false">'채집 확률표'!E36</f>
-        <v>0.0291970802919708</v>
+        <v>0.0300751879699248</v>
       </c>
       <c r="D37" s="21" t="n">
         <f aca="false">C37*규칙!$B$12*1</f>
-        <v>0.0437956204379562</v>
+        <v>0.0451127819548872</v>
       </c>
       <c r="E37" s="22" t="n">
         <f aca="false">D37*$B$2</f>
-        <v>0.306569343065693</v>
+        <v>0.315789473684211</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4556,15 +4556,15 @@
       </c>
       <c r="C39" s="20" t="n">
         <f aca="false">'채집 확률표'!E39</f>
-        <v>0.310077519379845</v>
+        <v>0.2</v>
       </c>
       <c r="D39" s="21" t="n">
         <f aca="false">C39*규칙!$B$12*규칙!$B$8</f>
-        <v>0.697674418604651</v>
+        <v>0.45</v>
       </c>
       <c r="E39" s="22" t="n">
         <f aca="false">D39*$B$2</f>
-        <v>4.88372093023256</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4576,15 +4576,15 @@
       </c>
       <c r="C40" s="20" t="n">
         <f aca="false">'채집 확률표'!E40</f>
-        <v>0.108527131782946</v>
+        <v>0.0692307692307692</v>
       </c>
       <c r="D40" s="21" t="n">
         <f aca="false">C40*규칙!$B$12*1</f>
-        <v>0.162790697674419</v>
+        <v>0.103846153846154</v>
       </c>
       <c r="E40" s="22" t="n">
         <f aca="false">D40*$B$2</f>
-        <v>1.13953488372093</v>
+        <v>0.726923076923077</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4596,15 +4596,15 @@
       </c>
       <c r="C41" s="20" t="n">
         <f aca="false">'채집 확률표'!E41</f>
-        <v>0.0387596899224806</v>
+        <v>0.0384615384615385</v>
       </c>
       <c r="D41" s="21" t="n">
         <f aca="false">C41*규칙!$B$12*1</f>
-        <v>0.0581395348837209</v>
+        <v>0.0576923076923077</v>
       </c>
       <c r="E41" s="22" t="n">
         <f aca="false">D41*$B$2</f>
-        <v>0.406976744186047</v>
+        <v>0.403846153846154</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4616,15 +4616,15 @@
       </c>
       <c r="C42" s="20" t="n">
         <f aca="false">'채집 확률표'!E42</f>
-        <v>0.0465116279069767</v>
+        <v>0.0461538461538462</v>
       </c>
       <c r="D42" s="21" t="n">
         <f aca="false">C42*규칙!$B$12*1</f>
-        <v>0.0697674418604651</v>
+        <v>0.0692307692307692</v>
       </c>
       <c r="E42" s="22" t="n">
         <f aca="false">D42*$B$2</f>
-        <v>0.488372093023256</v>
+        <v>0.484615384615385</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4636,15 +4636,15 @@
       </c>
       <c r="C43" s="20" t="n">
         <f aca="false">'채집 확률표'!E43</f>
-        <v>0.209302325581395</v>
+        <v>0.138461538461538</v>
       </c>
       <c r="D43" s="21" t="n">
         <f aca="false">C43*규칙!$B$12*규칙!$B$8</f>
-        <v>0.47093023255814</v>
+        <v>0.311538461538462</v>
       </c>
       <c r="E43" s="22" t="n">
         <f aca="false">D43*$B$2</f>
-        <v>3.29651162790698</v>
+        <v>2.18076923076923</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4656,15 +4656,15 @@
       </c>
       <c r="C44" s="20" t="n">
         <f aca="false">'채집 확률표'!E44</f>
-        <v>0.108527131782946</v>
+        <v>0.2</v>
       </c>
       <c r="D44" s="21" t="n">
         <f aca="false">C44*규칙!$B$12*1</f>
-        <v>0.162790697674419</v>
+        <v>0.3</v>
       </c>
       <c r="E44" s="22" t="n">
         <f aca="false">D44*$B$2</f>
-        <v>1.13953488372093</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4676,15 +4676,15 @@
       </c>
       <c r="C45" s="20" t="n">
         <f aca="false">'채집 확률표'!E45</f>
-        <v>0.0775193798449612</v>
+        <v>0.153846153846154</v>
       </c>
       <c r="D45" s="21" t="n">
         <f aca="false">C45*규칙!$B$12*1</f>
-        <v>0.116279069767442</v>
+        <v>0.230769230769231</v>
       </c>
       <c r="E45" s="22" t="n">
         <f aca="false">D45*$B$2</f>
-        <v>0.813953488372093</v>
+        <v>1.61538461538462</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4696,15 +4696,15 @@
       </c>
       <c r="C46" s="20" t="n">
         <f aca="false">'채집 확률표'!E46</f>
-        <v>0.0387596899224806</v>
+        <v>0.0923076923076923</v>
       </c>
       <c r="D46" s="21" t="n">
         <f aca="false">C46*규칙!$B$12*1</f>
-        <v>0.0581395348837209</v>
+        <v>0.138461538461538</v>
       </c>
       <c r="E46" s="22" t="n">
         <f aca="false">D46*$B$2</f>
-        <v>0.406976744186047</v>
+        <v>0.969230769230769</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4716,15 +4716,15 @@
       </c>
       <c r="C47" s="20" t="n">
         <f aca="false">'채집 확률표'!E47</f>
-        <v>0.0310077519379845</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="D47" s="21" t="n">
         <f aca="false">C47*규칙!$B$12*1</f>
-        <v>0.0465116279069767</v>
+        <v>0.0461538461538462</v>
       </c>
       <c r="E47" s="22" t="n">
         <f aca="false">D47*$B$2</f>
-        <v>0.325581395348837</v>
+        <v>0.323076923076923</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4736,15 +4736,15 @@
       </c>
       <c r="C48" s="20" t="n">
         <f aca="false">'채집 확률표'!E48</f>
-        <v>0.0310077519379845</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="D48" s="21" t="n">
         <f aca="false">C48*규칙!$B$12*1</f>
-        <v>0.0465116279069767</v>
+        <v>0.0461538461538462</v>
       </c>
       <c r="E48" s="22" t="n">
         <f aca="false">D48*$B$2</f>
-        <v>0.325581395348837</v>
+        <v>0.323076923076923</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4756,15 +4756,15 @@
       </c>
       <c r="C50" s="20" t="n">
         <f aca="false">'채집 확률표'!E51</f>
-        <v>0.233576642335766</v>
+        <v>0.147887323943662</v>
       </c>
       <c r="D50" s="21" t="n">
         <f aca="false">C50*규칙!$B$12*1</f>
-        <v>0.35036496350365</v>
+        <v>0.221830985915493</v>
       </c>
       <c r="E50" s="22" t="n">
         <f aca="false">D50*$B$2</f>
-        <v>2.45255474452555</v>
+        <v>1.55281690140845</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4776,15 +4776,15 @@
       </c>
       <c r="C51" s="20" t="n">
         <f aca="false">'채집 확률표'!E52</f>
-        <v>0.218978102189781</v>
+        <v>0.140845070422535</v>
       </c>
       <c r="D51" s="21" t="n">
         <f aca="false">C51*규칙!$B$12*규칙!$B$8</f>
-        <v>0.492700729927007</v>
+        <v>0.316901408450704</v>
       </c>
       <c r="E51" s="22" t="n">
         <f aca="false">D51*$B$2</f>
-        <v>3.44890510948905</v>
+        <v>2.21830985915493</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4796,15 +4796,15 @@
       </c>
       <c r="C52" s="20" t="n">
         <f aca="false">'채집 확률표'!E53</f>
-        <v>0.102189781021898</v>
+        <v>0.0985915492957746</v>
       </c>
       <c r="D52" s="21" t="n">
         <f aca="false">C52*규칙!$B$12*1</f>
-        <v>0.153284671532847</v>
+        <v>0.147887323943662</v>
       </c>
       <c r="E52" s="22" t="n">
         <f aca="false">D52*$B$2</f>
-        <v>1.07299270072993</v>
+        <v>1.03521126760563</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4816,15 +4816,15 @@
       </c>
       <c r="C53" s="20" t="n">
         <f aca="false">'채집 확률표'!E54</f>
-        <v>0.131386861313869</v>
+        <v>0.0845070422535211</v>
       </c>
       <c r="D53" s="21" t="n">
         <f aca="false">C53*규칙!$B$12*규칙!$B$8</f>
-        <v>0.295620437956204</v>
+        <v>0.190140845070423</v>
       </c>
       <c r="E53" s="22" t="n">
         <f aca="false">D53*$B$2</f>
-        <v>2.06934306569343</v>
+        <v>1.33098591549296</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4836,15 +4836,15 @@
       </c>
       <c r="C54" s="20" t="n">
         <f aca="false">'채집 확률표'!E55</f>
-        <v>0.0437956204379562</v>
+        <v>0.0633802816901408</v>
       </c>
       <c r="D54" s="21" t="n">
         <f aca="false">C54*규칙!$B$12*1</f>
-        <v>0.0656934306569343</v>
+        <v>0.0950704225352113</v>
       </c>
       <c r="E54" s="22" t="n">
         <f aca="false">D54*$B$2</f>
-        <v>0.45985401459854</v>
+        <v>0.665492957746479</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4856,15 +4856,15 @@
       </c>
       <c r="C55" s="20" t="n">
         <f aca="false">'채집 확률표'!E56</f>
-        <v>0.102189781021898</v>
+        <v>0.183098591549296</v>
       </c>
       <c r="D55" s="21" t="n">
         <f aca="false">C55*규칙!$B$12*1</f>
-        <v>0.153284671532847</v>
+        <v>0.274647887323944</v>
       </c>
       <c r="E55" s="22" t="n">
         <f aca="false">D55*$B$2</f>
-        <v>1.07299270072993</v>
+        <v>1.92253521126761</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4876,15 +4876,15 @@
       </c>
       <c r="C56" s="20" t="n">
         <f aca="false">'채집 확률표'!E57</f>
-        <v>0.072992700729927</v>
+        <v>0.140845070422535</v>
       </c>
       <c r="D56" s="21" t="n">
         <f aca="false">C56*규칙!$B$12*1</f>
-        <v>0.109489051094891</v>
+        <v>0.211267605633803</v>
       </c>
       <c r="E56" s="22" t="n">
         <f aca="false">D56*$B$2</f>
-        <v>0.766423357664234</v>
+        <v>1.47887323943662</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4896,15 +4896,15 @@
       </c>
       <c r="C57" s="20" t="n">
         <f aca="false">'채집 확률표'!E58</f>
-        <v>0.0364963503649635</v>
+        <v>0.0845070422535211</v>
       </c>
       <c r="D57" s="21" t="n">
         <f aca="false">C57*규칙!$B$12*1</f>
-        <v>0.0547445255474453</v>
+        <v>0.126760563380282</v>
       </c>
       <c r="E57" s="22" t="n">
         <f aca="false">D57*$B$2</f>
-        <v>0.383211678832117</v>
+        <v>0.887323943661972</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4916,15 +4916,15 @@
       </c>
       <c r="C58" s="20" t="n">
         <f aca="false">'채집 확률표'!E59</f>
-        <v>0.0291970802919708</v>
+        <v>0.028169014084507</v>
       </c>
       <c r="D58" s="21" t="n">
         <f aca="false">C58*규칙!$B$12*1</f>
-        <v>0.0437956204379562</v>
+        <v>0.0422535211267606</v>
       </c>
       <c r="E58" s="22" t="n">
         <f aca="false">D58*$B$2</f>
-        <v>0.306569343065693</v>
+        <v>0.295774647887324</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4936,15 +4936,15 @@
       </c>
       <c r="C59" s="20" t="n">
         <f aca="false">'채집 확률표'!E60</f>
-        <v>0.0291970802919708</v>
+        <v>0.028169014084507</v>
       </c>
       <c r="D59" s="21" t="n">
         <f aca="false">C59*규칙!$B$12*1</f>
-        <v>0.0437956204379562</v>
+        <v>0.0422535211267606</v>
       </c>
       <c r="E59" s="22" t="n">
         <f aca="false">D59*$B$2</f>
-        <v>0.306569343065693</v>
+        <v>0.295774647887324</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4956,15 +4956,15 @@
       </c>
       <c r="C61" s="20" t="n">
         <f aca="false">'채집 확률표'!E63</f>
-        <v>0.35036496350365</v>
+        <v>0.208053691275168</v>
       </c>
       <c r="D61" s="21" t="n">
         <f aca="false">C61*규칙!$B$12*규칙!$B$8</f>
-        <v>0.788321167883212</v>
+        <v>0.468120805369128</v>
       </c>
       <c r="E61" s="22" t="n">
         <f aca="false">D61*$B$2</f>
-        <v>5.51824817518248</v>
+        <v>3.27684563758389</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4976,15 +4976,15 @@
       </c>
       <c r="C62" s="20" t="n">
         <f aca="false">'채집 확률표'!E64</f>
-        <v>0.102189781021898</v>
+        <v>0.140939597315436</v>
       </c>
       <c r="D62" s="21" t="n">
         <f aca="false">C62*규칙!$B$12*1</f>
-        <v>0.153284671532847</v>
+        <v>0.211409395973154</v>
       </c>
       <c r="E62" s="22" t="n">
         <f aca="false">D62*$B$2</f>
-        <v>1.07299270072993</v>
+        <v>1.47986577181208</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4996,15 +4996,15 @@
       </c>
       <c r="C63" s="20" t="n">
         <f aca="false">'채집 확률표'!E65</f>
-        <v>0.145985401459854</v>
+        <v>0.087248322147651</v>
       </c>
       <c r="D63" s="21" t="n">
         <f aca="false">C63*규칙!$B$12*1</f>
-        <v>0.218978102189781</v>
+        <v>0.130872483221477</v>
       </c>
       <c r="E63" s="22" t="n">
         <f aca="false">D63*$B$2</f>
-        <v>1.53284671532847</v>
+        <v>0.916107382550336</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5016,15 +5016,15 @@
       </c>
       <c r="C64" s="20" t="n">
         <f aca="false">'채집 확률표'!E66</f>
-        <v>0.131386861313869</v>
+        <v>0.120805369127517</v>
       </c>
       <c r="D64" s="21" t="n">
         <f aca="false">C64*규칙!$B$12*1</f>
-        <v>0.197080291970803</v>
+        <v>0.181208053691275</v>
       </c>
       <c r="E64" s="22" t="n">
         <f aca="false">D64*$B$2</f>
-        <v>1.37956204379562</v>
+        <v>1.26845637583893</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5036,15 +5036,15 @@
       </c>
       <c r="C65" s="20" t="n">
         <f aca="false">'채집 확률표'!E67</f>
-        <v>0.102189781021898</v>
+        <v>0.174496644295302</v>
       </c>
       <c r="D65" s="21" t="n">
         <f aca="false">C65*규칙!$B$12*1</f>
-        <v>0.153284671532847</v>
+        <v>0.261744966442953</v>
       </c>
       <c r="E65" s="22" t="n">
         <f aca="false">D65*$B$2</f>
-        <v>1.07299270072993</v>
+        <v>1.83221476510067</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5056,15 +5056,15 @@
       </c>
       <c r="C66" s="20" t="n">
         <f aca="false">'채집 확률표'!E68</f>
-        <v>0.072992700729927</v>
+        <v>0.134228187919463</v>
       </c>
       <c r="D66" s="21" t="n">
         <f aca="false">C66*규칙!$B$12*1</f>
-        <v>0.109489051094891</v>
+        <v>0.201342281879195</v>
       </c>
       <c r="E66" s="22" t="n">
         <f aca="false">D66*$B$2</f>
-        <v>0.766423357664234</v>
+        <v>1.40939597315436</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5076,15 +5076,15 @@
       </c>
       <c r="C67" s="20" t="n">
         <f aca="false">'채집 확률표'!E69</f>
-        <v>0.0364963503649635</v>
+        <v>0.0805369127516779</v>
       </c>
       <c r="D67" s="21" t="n">
         <f aca="false">C67*규칙!$B$12*1</f>
-        <v>0.0547445255474453</v>
+        <v>0.120805369127517</v>
       </c>
       <c r="E67" s="22" t="n">
         <f aca="false">D67*$B$2</f>
-        <v>0.383211678832117</v>
+        <v>0.845637583892617</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5096,15 +5096,15 @@
       </c>
       <c r="C68" s="20" t="n">
         <f aca="false">'채집 확률표'!E70</f>
-        <v>0.0291970802919708</v>
+        <v>0.0268456375838926</v>
       </c>
       <c r="D68" s="21" t="n">
         <f aca="false">C68*규칙!$B$12*1</f>
-        <v>0.0437956204379562</v>
+        <v>0.0402684563758389</v>
       </c>
       <c r="E68" s="22" t="n">
         <f aca="false">D68*$B$2</f>
-        <v>0.306569343065693</v>
+        <v>0.281879194630872</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5116,15 +5116,15 @@
       </c>
       <c r="C69" s="20" t="n">
         <f aca="false">'채집 확률표'!E71</f>
-        <v>0.0291970802919708</v>
+        <v>0.0268456375838926</v>
       </c>
       <c r="D69" s="21" t="n">
         <f aca="false">C69*규칙!$B$12*1</f>
-        <v>0.0437956204379562</v>
+        <v>0.0402684563758389</v>
       </c>
       <c r="E69" s="22" t="n">
         <f aca="false">D69*$B$2</f>
-        <v>0.306569343065693</v>
+        <v>0.281879194630872</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
